--- a/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
+++ b/debug/judgements_intro/excel_overviews/gpt-4.1_vs_Qwen2.5-3B-Instruct/Llama-3.3-70B-Instruct/aae/total_votes_file.xlsx
@@ -433,10 +433,10 @@
         <v>58</v>
       </c>
       <c r="D2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G2">
         <v>0</v>
@@ -450,10 +450,10 @@
         <v>8</v>
       </c>
       <c r="C3">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="D3">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="E3">
         <v>0</v>
